--- a/AAII_Financials/Quarterly/VNJA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNJA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/VNJA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNJA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>VNJA</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -794,14 +801,14 @@
         <v>4</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -874,8 +881,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,8 +976,14 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,8 +1071,14 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1296,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1301,14 +1340,14 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1325,17 +1364,17 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1352,8 +1391,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,8 +1522,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1528,14 +1581,14 @@
         <v>0</v>
       </c>
       <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
       <c r="X17" s="3">
         <v>0</v>
       </c>
@@ -1560,8 +1613,14 @@
       <c r="AE17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1569,14 +1628,14 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>100</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
         <v>0</v>
       </c>
@@ -1617,14 +1676,14 @@
         <v>0</v>
       </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
         <v>0</v>
       </c>
@@ -1649,8 +1708,14 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1691,14 +1758,14 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1771,8 +1838,14 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1800,11 +1873,11 @@
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
@@ -1860,8 +1933,14 @@
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1949,8 +2028,14 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2038,8 +2123,14 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2127,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,8 +2313,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2305,8 +2408,14 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2394,8 +2503,14 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2759,14 +2898,14 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2839,8 +2978,14 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2928,8 +3073,14 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,8 +3168,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3106,102 +3263,114 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,13 +3437,15 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -3314,19 +3487,19 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3">
         <v>100</v>
       </c>
       <c r="U41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
@@ -3355,8 +3528,14 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,13 +3623,19 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>100</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -3459,13 +3644,13 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
@@ -3476,11 +3661,11 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3533,8 +3718,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3622,8 +3813,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3711,8 +3908,14 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3726,10 +3929,10 @@
         <v>100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -3759,19 +3962,19 @@
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3">
         <v>100</v>
       </c>
       <c r="U46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
@@ -3800,8 +4003,14 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3854,10 +4063,10 @@
         <v>700</v>
       </c>
       <c r="T47" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="U47" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3889,8 +4098,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3943,19 +4158,19 @@
         <v>0</v>
       </c>
       <c r="T48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="U48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3">
         <v>700</v>
       </c>
       <c r="W48" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,8 +4478,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4271,8 +4510,8 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4280,8 +4519,8 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -4295,11 +4534,11 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,8 +4668,14 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4486,17 +4737,17 @@
         <v>800</v>
       </c>
       <c r="W54" s="3">
+        <v>800</v>
+      </c>
+      <c r="X54" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y54" s="3">
         <v>100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>100</v>
       </c>
-      <c r="Y54" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>0</v>
-      </c>
       <c r="AA54" s="3">
         <v>0</v>
       </c>
@@ -4512,8 +4763,14 @@
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,8 +4837,10 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4667,8 +4928,14 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4756,8 +5023,14 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4845,8 +5118,14 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4934,8 +5213,14 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5023,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5049,8 +5340,8 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5058,8 +5349,8 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
@@ -5073,11 +5364,11 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5112,8 +5403,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,8 +5688,14 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5468,8 +5783,14 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,8 +6198,14 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5872,10 +6219,10 @@
         <v>-100</v>
       </c>
       <c r="G72" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H72" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I72" s="3">
         <v>-200</v>
@@ -5905,10 +6252,10 @@
         <v>-200</v>
       </c>
       <c r="R72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="S72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="T72" s="3">
         <v>-100</v>
@@ -5946,8 +6293,14 @@
       <c r="AE72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,8 +6578,14 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6276,17 +6647,17 @@
         <v>800</v>
       </c>
       <c r="W76" s="3">
+        <v>800</v>
+      </c>
+      <c r="X76" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y76" s="3">
         <v>100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>100</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
       <c r="AA76" s="3">
         <v>0</v>
       </c>
@@ -6302,8 +6673,14 @@
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,102 +6768,114 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6574,8 +6963,14 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6696,8 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,13 +7568,19 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -7230,8 +7663,14 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7352,8 +7793,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,8 +7983,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7619,8 +8078,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,8 +8493,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8061,23 +8552,23 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>4</v>
@@ -8085,20 +8576,26 @@
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8186,13 +8683,19 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
@@ -8273,6 +8776,12 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VNJA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNJA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>VNJA</t>
   </si>
@@ -656,149 +656,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -807,11 +811,11 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -887,8 +891,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1346,11 +1366,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1370,14 +1390,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1397,8 +1417,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,8 +1550,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1587,11 +1614,11 @@
         <v>0</v>
       </c>
       <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
         <v>100</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
@@ -1619,13 +1646,16 @@
       <c r="AG17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>100</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -1634,11 +1664,11 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
         <v>0</v>
       </c>
@@ -1682,11 +1712,11 @@
         <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
         <v>0</v>
       </c>
@@ -1714,8 +1744,11 @@
       <c r="AG18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,13 +1782,14 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1764,11 +1798,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1844,13 +1878,16 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -1879,8 +1916,8 @@
       <c r="M21" s="3">
         <v>0</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
+      <c r="N21" s="3">
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
@@ -1939,8 +1976,11 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,8 +2074,11 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2129,8 +2172,11 @@
       <c r="AG23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,8 +2368,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2414,8 +2466,11 @@
       <c r="AG26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2509,8 +2564,11 @@
       <c r="AG27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,13 +2956,16 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2904,11 +2974,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2984,8 +3054,11 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3079,8 +3152,11 @@
       <c r="AG33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,8 +3250,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3269,108 +3348,114 @@
       <c r="AG35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,8 +3525,9 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3448,7 +3535,7 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -3493,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U41" s="3">
         <v>100</v>
@@ -3502,7 +3589,7 @@
         <v>100</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,16 +3719,19 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
         <v>100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -3650,10 +3743,10 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -3667,8 +3760,8 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +3915,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,8 +4013,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3935,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -3968,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U46" s="3">
         <v>100</v>
@@ -3977,7 +4079,7 @@
         <v>100</v>
       </c>
       <c r="W46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X46" s="3">
         <v>0</v>
@@ -4009,8 +4111,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4069,7 +4174,7 @@
         <v>700</v>
       </c>
       <c r="V47" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4104,8 +4209,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4164,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="W48" s="3">
         <v>700</v>
@@ -4173,7 +4281,7 @@
         <v>700</v>
       </c>
       <c r="Y48" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4516,14 +4636,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -4540,8 +4660,8 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,13 +4797,16 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E54" s="3">
         <v>800</v>
@@ -4743,13 +4869,13 @@
         <v>800</v>
       </c>
       <c r="Y54" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="Z54" s="3">
         <v>100</v>
       </c>
       <c r="AA54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB54" s="3">
         <v>0</v>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4969,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4934,8 +5065,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,8 +5163,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5124,8 +5261,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,8 +5359,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5314,8 +5457,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5346,14 +5492,14 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
@@ -5370,8 +5516,8 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,8 +5849,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,8 +6375,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6225,7 +6399,7 @@
         <v>-100</v>
       </c>
       <c r="I72" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="J72" s="3">
         <v>-200</v>
@@ -6258,7 +6432,7 @@
         <v>-200</v>
       </c>
       <c r="T72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="U72" s="3">
         <v>-100</v>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,13 +6767,16 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E76" s="3">
         <v>800</v>
@@ -6653,13 +6839,13 @@
         <v>800</v>
       </c>
       <c r="Y76" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="Z76" s="3">
         <v>100</v>
       </c>
       <c r="AA76" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB76" s="3">
         <v>0</v>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,108 +6963,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6969,8 +7164,11 @@
       <c r="AG81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,17 +7788,20 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
@@ -7669,8 +7886,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8742,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8558,8 +8804,8 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
@@ -8567,11 +8813,11 @@
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
@@ -8582,8 +8828,8 @@
       <c r="AC100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -8591,11 +8837,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,17 +8938,20 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
@@ -8782,6 +9034,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>
